--- a/Ahmedabad-June-2025.xlsx
+++ b/Ahmedabad-June-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="67">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Ahmedabad</t>
   </si>
   <si>
@@ -163,7 +166,7 @@
     <t>AMAZE</t>
   </si>
   <si>
-    <t>Crysta</t>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>CITROEN</t>
@@ -178,13 +181,49 @@
     <t>INVICTO</t>
   </si>
   <si>
-    <t>-</t>
+    <t>15/05/2025</t>
+  </si>
+  <si>
+    <t>29/05/2018</t>
+  </si>
+  <si>
+    <t>28/02/2019</t>
+  </si>
+  <si>
+    <t>30/03/2019</t>
+  </si>
+  <si>
+    <t>26/04/2019</t>
+  </si>
+  <si>
+    <t>29/03/2022</t>
+  </si>
+  <si>
+    <t>18/07/2022</t>
+  </si>
+  <si>
+    <t>17/10/2023</t>
+  </si>
+  <si>
+    <t>27/02/2025</t>
+  </si>
+  <si>
+    <t>26/07/2024</t>
+  </si>
+  <si>
+    <t>21/04/2025</t>
+  </si>
+  <si>
+    <t>16/08/2024</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -237,11 +276,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -536,10 +576,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:AA21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -618,28 +658,31 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2025</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G2">
-        <v>45792</v>
+        <v>49</v>
+      </c>
+      <c r="G2" t="s">
+        <v>55</v>
       </c>
       <c r="H2">
         <v>2428</v>
@@ -699,27 +742,27 @@
         <v>32.58</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2025</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3">
-        <v>45792</v>
+        <v>49</v>
+      </c>
+      <c r="G3" t="s">
+        <v>55</v>
       </c>
       <c r="H3">
         <v>2738</v>
@@ -779,27 +822,27 @@
         <v>30.33</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2025</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H4">
         <v>198682</v>
@@ -859,27 +902,27 @@
         <v>45.99</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2025</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H5">
         <v>341166</v>
@@ -939,27 +982,27 @@
         <v>34.29</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2025</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H6">
         <v>352304</v>
@@ -1019,27 +1062,27 @@
         <v>48.31</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>2025</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H7">
         <v>320924</v>
@@ -1099,27 +1142,27 @@
         <v>38.73</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:27">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>2025</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G8" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H8">
         <v>350801</v>
@@ -1179,27 +1222,27 @@
         <v>40.79</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>2025</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9">
-        <v>43899</v>
+        <v>50</v>
+      </c>
+      <c r="G9" s="2">
+        <v>44077</v>
       </c>
       <c r="H9">
         <v>147571</v>
@@ -1259,27 +1302,27 @@
         <v>79.51000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:27">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>2025</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10">
-        <v>44470</v>
+        <v>50</v>
+      </c>
+      <c r="G10" s="2">
+        <v>44206</v>
       </c>
       <c r="H10">
         <v>97486</v>
@@ -1339,27 +1382,27 @@
         <v>47.58</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:27">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>2025</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11">
-        <v>44649</v>
+        <v>50</v>
+      </c>
+      <c r="G11" t="s">
+        <v>60</v>
       </c>
       <c r="H11">
         <v>110316</v>
@@ -1419,27 +1462,27 @@
         <v>50.12</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:27">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>2025</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12">
-        <v>44658</v>
+        <v>50</v>
+      </c>
+      <c r="G12" s="2">
+        <v>44746</v>
       </c>
       <c r="H12">
         <v>44080</v>
@@ -1499,27 +1542,27 @@
         <v>59.59</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:27">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>2025</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>49</v>
-      </c>
-      <c r="G13">
-        <v>44760</v>
+        <v>50</v>
+      </c>
+      <c r="G13" t="s">
+        <v>61</v>
       </c>
       <c r="H13">
         <v>67611</v>
@@ -1579,27 +1622,27 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:27">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14">
         <v>2025</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>49</v>
-      </c>
-      <c r="G14">
-        <v>45216</v>
+        <v>50</v>
+      </c>
+      <c r="G14" t="s">
+        <v>62</v>
       </c>
       <c r="H14">
         <v>124753</v>
@@ -1659,27 +1702,27 @@
         <v>29.43</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:27">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>2025</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
-        <v>49</v>
-      </c>
-      <c r="G15">
-        <v>45715</v>
+        <v>50</v>
+      </c>
+      <c r="G15" t="s">
+        <v>63</v>
       </c>
       <c r="H15">
         <v>18846</v>
@@ -1739,27 +1782,27 @@
         <v>17.06</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:27">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>2025</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" t="s">
-        <v>50</v>
-      </c>
-      <c r="G16">
-        <v>45499</v>
+        <v>51</v>
+      </c>
+      <c r="G16" t="s">
+        <v>64</v>
       </c>
       <c r="H16">
         <v>22771</v>
@@ -1824,22 +1867,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>2025</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>50</v>
-      </c>
-      <c r="G17">
-        <v>45499</v>
+        <v>51</v>
+      </c>
+      <c r="G17" t="s">
+        <v>64</v>
       </c>
       <c r="H17">
         <v>19570</v>
@@ -1904,22 +1947,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>2025</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>51</v>
-      </c>
-      <c r="G18">
-        <v>44987</v>
+        <v>52</v>
+      </c>
+      <c r="G18" s="2">
+        <v>44960</v>
       </c>
       <c r="H18">
         <v>68249</v>
@@ -1984,22 +2027,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19">
         <v>2025</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>52</v>
-      </c>
-      <c r="G19">
-        <v>45768</v>
+        <v>53</v>
+      </c>
+      <c r="G19" t="s">
+        <v>65</v>
       </c>
       <c r="H19">
         <v>1972</v>
@@ -2064,22 +2107,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20">
         <v>2025</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>52</v>
-      </c>
-      <c r="G20">
-        <v>45768</v>
+        <v>53</v>
+      </c>
+      <c r="G20" t="s">
+        <v>65</v>
       </c>
       <c r="H20">
         <v>1407</v>
@@ -2144,22 +2187,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21">
         <v>2025</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
-        <v>53</v>
-      </c>
-      <c r="G21">
-        <v>45520</v>
+        <v>54</v>
+      </c>
+      <c r="G21" t="s">
+        <v>66</v>
       </c>
       <c r="H21">
         <v>50827</v>
